--- a/artfynd/A 57149-2025 artfynd.xlsx
+++ b/artfynd/A 57149-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130238781</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>130238777</v>
       </c>
       <c r="B3" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57149-2025 artfynd.xlsx
+++ b/artfynd/A 57149-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>130238777</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57149-2025 artfynd.xlsx
+++ b/artfynd/A 57149-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130238781</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>130238777</v>
       </c>
       <c r="B3" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57149-2025 artfynd.xlsx
+++ b/artfynd/A 57149-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>130238777</v>
       </c>
       <c r="B3" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57149-2025 artfynd.xlsx
+++ b/artfynd/A 57149-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>130238777</v>
       </c>
       <c r="B3" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57149-2025 artfynd.xlsx
+++ b/artfynd/A 57149-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130238781</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>130238777</v>
       </c>
       <c r="B3" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 57149-2025 artfynd.xlsx
+++ b/artfynd/A 57149-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>130238777</v>
       </c>
       <c r="B3" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
